--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/5.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/5.xlsx
@@ -426,13 +426,13 @@
         <v>-16.27703438141167</v>
       </c>
       <c r="E2">
-        <v>-5.560773433744471</v>
+        <v>-6.054218603990272</v>
       </c>
       <c r="F2">
-        <v>-2.483678392080612</v>
+        <v>-1.345656485338415</v>
       </c>
       <c r="G2">
-        <v>-7.433383213272878</v>
+        <v>-7.11043554372765</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.49405956918889</v>
       </c>
       <c r="E3">
-        <v>-5.890844847215548</v>
+        <v>-6.540703509686283</v>
       </c>
       <c r="F3">
-        <v>-2.593492573567534</v>
+        <v>-1.701412120349107</v>
       </c>
       <c r="G3">
-        <v>-7.444526241688751</v>
+        <v>-8.339666451656186</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.73875754204824</v>
       </c>
       <c r="E4">
-        <v>-6.893992409394686</v>
+        <v>-6.888861648343995</v>
       </c>
       <c r="F4">
-        <v>-2.603586230370646</v>
+        <v>-1.367498877015432</v>
       </c>
       <c r="G4">
-        <v>-6.733823495577704</v>
+        <v>-7.440529713829348</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.11158933114968</v>
       </c>
       <c r="E5">
-        <v>-7.338072684482872</v>
+        <v>-8.640556907043027</v>
       </c>
       <c r="F5">
-        <v>-2.374250229803395</v>
+        <v>-1.383447434621531</v>
       </c>
       <c r="G5">
-        <v>-7.204606602483714</v>
+        <v>-6.938873593270523</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.58258278090561</v>
       </c>
       <c r="E6">
-        <v>-8.098534796116947</v>
+        <v>-8.911400408967785</v>
       </c>
       <c r="F6">
-        <v>-2.198232925484736</v>
+        <v>-1.149317671894279</v>
       </c>
       <c r="G6">
-        <v>-7.278968926685409</v>
+        <v>-7.760012413407802</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.1625294359203</v>
       </c>
       <c r="E7">
-        <v>-8.000452577584815</v>
+        <v>-9.455030128166587</v>
       </c>
       <c r="F7">
-        <v>-2.272173828226023</v>
+        <v>-1.357582490836519</v>
       </c>
       <c r="G7">
-        <v>-7.550339074537725</v>
+        <v>-7.117162047924512</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.83345973876025</v>
       </c>
       <c r="E8">
-        <v>-9.202685442563164</v>
+        <v>-9.190463091216461</v>
       </c>
       <c r="F8">
-        <v>-1.999752782304363</v>
+        <v>-0.824667232858708</v>
       </c>
       <c r="G8">
-        <v>-6.917834400631364</v>
+        <v>-6.974104069154282</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.58849013748</v>
       </c>
       <c r="E9">
-        <v>-9.62583058231389</v>
+        <v>-11.82161517304912</v>
       </c>
       <c r="F9">
-        <v>-2.218978558720447</v>
+        <v>-0.8466960072013552</v>
       </c>
       <c r="G9">
-        <v>-6.66146599774883</v>
+        <v>-6.820690555142444</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.41092294931987</v>
       </c>
       <c r="E10">
-        <v>-9.899721747245808</v>
+        <v>-11.25830470581299</v>
       </c>
       <c r="F10">
-        <v>-1.847507137343842</v>
+        <v>-0.8245769408118029</v>
       </c>
       <c r="G10">
-        <v>-6.97121659418197</v>
+        <v>-6.429168636226382</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.28348894928124</v>
       </c>
       <c r="E11">
-        <v>-11.07861032871462</v>
+        <v>-11.20182557798932</v>
       </c>
       <c r="F11">
-        <v>-1.810325866469187</v>
+        <v>-0.2058270809233093</v>
       </c>
       <c r="G11">
-        <v>-6.526000765667154</v>
+        <v>-6.202613412432962</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.19429295839796</v>
       </c>
       <c r="E12">
-        <v>-11.1707013761346</v>
+        <v>-11.24272222675259</v>
       </c>
       <c r="F12">
-        <v>-1.392162688066385</v>
+        <v>-0.192611307379046</v>
       </c>
       <c r="G12">
-        <v>-6.357181916433724</v>
+        <v>-6.568522115855998</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.118578424808</v>
       </c>
       <c r="E13">
-        <v>-11.52715567917437</v>
+        <v>-12.49302484332236</v>
       </c>
       <c r="F13">
-        <v>-1.327345423899532</v>
+        <v>0.02853959488114361</v>
       </c>
       <c r="G13">
-        <v>-6.384822926850486</v>
+        <v>-6.255929981552379</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.04607892978479</v>
       </c>
       <c r="E14">
-        <v>-12.59496079323502</v>
+        <v>-13.55002954687472</v>
       </c>
       <c r="F14">
-        <v>-0.9534485427675303</v>
+        <v>0.2329359380523104</v>
       </c>
       <c r="G14">
-        <v>-5.719496193685</v>
+        <v>-5.223670803837309</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.95425515328145</v>
       </c>
       <c r="E15">
-        <v>-13.25791127406193</v>
+        <v>-13.35351188883786</v>
       </c>
       <c r="F15">
-        <v>-1.091688151681517</v>
+        <v>0.2969322901229891</v>
       </c>
       <c r="G15">
-        <v>-4.923379969160048</v>
+        <v>-6.579084368055852</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.83717903321636</v>
       </c>
       <c r="E16">
-        <v>-14.38311932464381</v>
+        <v>-15.12359728048204</v>
       </c>
       <c r="F16">
-        <v>-0.5092622024057822</v>
+        <v>0.2511152890741484</v>
       </c>
       <c r="G16">
-        <v>-4.199115934343816</v>
+        <v>-5.281354678852347</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.68621580346526</v>
       </c>
       <c r="E17">
-        <v>-14.96927594324865</v>
+        <v>-16.14256280236997</v>
       </c>
       <c r="F17">
-        <v>-0.3714334637235837</v>
+        <v>0.5519327695637748</v>
       </c>
       <c r="G17">
-        <v>-4.099209300301843</v>
+        <v>-3.898605257822071</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.50851078151151</v>
       </c>
       <c r="E18">
-        <v>-16.27791436198523</v>
+        <v>-16.07612556020344</v>
       </c>
       <c r="F18">
-        <v>-0.3565220221057898</v>
+        <v>0.6868729911124115</v>
       </c>
       <c r="G18">
-        <v>-4.100639912901761</v>
+        <v>-4.264159589316688</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.31126141604014</v>
       </c>
       <c r="E19">
-        <v>-16.18067443961852</v>
+        <v>-17.66970462045066</v>
       </c>
       <c r="F19">
-        <v>0.06185073324992013</v>
+        <v>1.171007349474166</v>
       </c>
       <c r="G19">
-        <v>-3.427320124017467</v>
+        <v>-3.69516295869338</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.11327344236656</v>
       </c>
       <c r="E20">
-        <v>-17.34227783580006</v>
+        <v>-17.94557925699793</v>
       </c>
       <c r="F20">
-        <v>0.3441873369830896</v>
+        <v>1.626261506704718</v>
       </c>
       <c r="G20">
-        <v>-3.448894155770816</v>
+        <v>-3.28820289234013</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.92895756745782</v>
       </c>
       <c r="E21">
-        <v>-18.07855789623317</v>
+        <v>-20.22317073068173</v>
       </c>
       <c r="F21">
-        <v>0.7099943820593513</v>
+        <v>1.943456639115094</v>
       </c>
       <c r="G21">
-        <v>-3.092504276091729</v>
+        <v>-3.272498965956628</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.77825363638036</v>
       </c>
       <c r="E22">
-        <v>-19.27293838728222</v>
+        <v>-19.77863307971877</v>
       </c>
       <c r="F22">
-        <v>0.9186800116422139</v>
+        <v>1.753478858957055</v>
       </c>
       <c r="G22">
-        <v>-3.253946939259527</v>
+        <v>-2.957278573183893</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.67114654506394</v>
       </c>
       <c r="E23">
-        <v>-19.91442842978678</v>
+        <v>-19.87852215937996</v>
       </c>
       <c r="F23">
-        <v>1.126908382418731</v>
+        <v>2.304240464260779</v>
       </c>
       <c r="G23">
-        <v>-2.760963087282315</v>
+        <v>-2.327877934872767</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.61236015994155</v>
       </c>
       <c r="E24">
-        <v>-19.96829009963401</v>
+        <v>-21.80440969925804</v>
       </c>
       <c r="F24">
-        <v>1.089797522773313</v>
+        <v>2.048750419684939</v>
       </c>
       <c r="G24">
-        <v>-2.834380419674891</v>
+        <v>-3.698752615079413</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.598269088071</v>
       </c>
       <c r="E25">
-        <v>-20.73308143241942</v>
+        <v>-20.26553007654948</v>
       </c>
       <c r="F25">
-        <v>1.368276419511646</v>
+        <v>2.65841557426693</v>
       </c>
       <c r="G25">
-        <v>-2.474673224999204</v>
+        <v>-2.983577563982842</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.61087448537667</v>
       </c>
       <c r="E26">
-        <v>-20.15306995304299</v>
+        <v>-21.6985883186468</v>
       </c>
       <c r="F26">
-        <v>1.575292060410465</v>
+        <v>2.951723904250179</v>
       </c>
       <c r="G26">
-        <v>-3.365669252137061</v>
+        <v>-3.712996397868962</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.63267704369385</v>
       </c>
       <c r="E27">
-        <v>-20.45345269091978</v>
+        <v>-20.89283693846201</v>
       </c>
       <c r="F27">
-        <v>1.434598827249385</v>
+        <v>2.42012906391243</v>
       </c>
       <c r="G27">
-        <v>-3.271905064854368</v>
+        <v>-2.755260324212001</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.6329431366657</v>
       </c>
       <c r="E28">
-        <v>-20.36220846813923</v>
+        <v>-21.48254388068887</v>
       </c>
       <c r="F28">
-        <v>1.515265244934001</v>
+        <v>2.882957812674181</v>
       </c>
       <c r="G28">
-        <v>-3.675400161240844</v>
+        <v>-3.187433297028023</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.59285397100507</v>
       </c>
       <c r="E29">
-        <v>-20.38749093852406</v>
+        <v>-20.82270898997923</v>
       </c>
       <c r="F29">
-        <v>1.497248253923112</v>
+        <v>2.610130038357747</v>
       </c>
       <c r="G29">
-        <v>-3.478539992560399</v>
+        <v>-3.590416522851226</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.48865045860837</v>
       </c>
       <c r="E30">
-        <v>-20.86090666823393</v>
+        <v>-21.6586154785811</v>
       </c>
       <c r="F30">
-        <v>1.630741317619058</v>
+        <v>2.261877755281613</v>
       </c>
       <c r="G30">
-        <v>-3.317589512626517</v>
+        <v>-3.672141908232316</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.31224720174007</v>
       </c>
       <c r="E31">
-        <v>-20.1665965049039</v>
+        <v>-21.68791017693671</v>
       </c>
       <c r="F31">
-        <v>1.367401663534289</v>
+        <v>1.851494603525904</v>
       </c>
       <c r="G31">
-        <v>-4.000231251961193</v>
+        <v>-2.970836580667518</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.05741207253408</v>
       </c>
       <c r="E32">
-        <v>-19.54324300080006</v>
+        <v>-21.1566114924608</v>
       </c>
       <c r="F32">
-        <v>1.127524687766414</v>
+        <v>2.144416914299448</v>
       </c>
       <c r="G32">
-        <v>-4.090021879935398</v>
+        <v>-3.053457739534336</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.730563299999778</v>
       </c>
       <c r="E33">
-        <v>-19.2478959260198</v>
+        <v>-21.09274189505662</v>
       </c>
       <c r="F33">
-        <v>1.16314945629121</v>
+        <v>2.301975707781525</v>
       </c>
       <c r="G33">
-        <v>-3.889270182485451</v>
+        <v>-3.678799506776429</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.340793026849992</v>
       </c>
       <c r="E34">
-        <v>-19.36626117963229</v>
+        <v>-20.76197309658836</v>
       </c>
       <c r="F34">
-        <v>1.173578601892455</v>
+        <v>2.019717798951622</v>
       </c>
       <c r="G34">
-        <v>-3.747895470375216</v>
+        <v>-3.388992174981593</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.905318626642703</v>
       </c>
       <c r="E35">
-        <v>-19.29744648861173</v>
+        <v>-20.59078319367639</v>
       </c>
       <c r="F35">
-        <v>0.7642607306167469</v>
+        <v>1.343721952957863</v>
       </c>
       <c r="G35">
-        <v>-3.747564066997712</v>
+        <v>-3.849977554311101</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.443221170025588</v>
       </c>
       <c r="E36">
-        <v>-19.28553207349755</v>
+        <v>-20.92424643417922</v>
       </c>
       <c r="F36">
-        <v>0.8671423053096399</v>
+        <v>1.611866137978868</v>
       </c>
       <c r="G36">
-        <v>-3.91214357797634</v>
+        <v>-3.955603357531185</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.977599149003384</v>
       </c>
       <c r="E37">
-        <v>-18.50942408416698</v>
+        <v>-20.55280741064807</v>
       </c>
       <c r="F37">
-        <v>0.9441274582562148</v>
+        <v>1.670708388069328</v>
       </c>
       <c r="G37">
-        <v>-3.577918349931301</v>
+        <v>-3.127367255160828</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.532518280562155</v>
       </c>
       <c r="E38">
-        <v>-18.32969347927655</v>
+        <v>-20.33665428931395</v>
       </c>
       <c r="F38">
-        <v>0.8689216384908532</v>
+        <v>1.857781912113152</v>
       </c>
       <c r="G38">
-        <v>-3.236346466814666</v>
+        <v>-2.096692907458971</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.126920077942723</v>
       </c>
       <c r="E39">
-        <v>-17.63623466905996</v>
+        <v>-19.07221830536624</v>
       </c>
       <c r="F39">
-        <v>0.7386244162349078</v>
+        <v>1.576975302972953</v>
       </c>
       <c r="G39">
-        <v>-2.167459012831515</v>
+        <v>-1.576179606598017</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.781183564196297</v>
       </c>
       <c r="E40">
-        <v>-17.77304439730569</v>
+        <v>-19.64992479147276</v>
       </c>
       <c r="F40">
-        <v>0.6329785795188728</v>
+        <v>1.801482749949286</v>
       </c>
       <c r="G40">
-        <v>-2.698518159784523</v>
+        <v>-1.812401309105561</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.500937571901009</v>
       </c>
       <c r="E41">
-        <v>-17.51369869088641</v>
+        <v>-18.90730486742891</v>
       </c>
       <c r="F41">
-        <v>0.4766300308122858</v>
+        <v>1.594029731061789</v>
       </c>
       <c r="G41">
-        <v>-2.505848111035489</v>
+        <v>-0.9838108348067846</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.293844400790252</v>
       </c>
       <c r="E42">
-        <v>-17.38036683067857</v>
+        <v>-18.27716770926158</v>
       </c>
       <c r="F42">
-        <v>0.2947329746685564</v>
+        <v>1.061744032310105</v>
       </c>
       <c r="G42">
-        <v>-1.980317822410145</v>
+        <v>-2.590123005568267</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.150826261298674</v>
       </c>
       <c r="E43">
-        <v>-17.13913049181597</v>
+        <v>-17.9421376167521</v>
       </c>
       <c r="F43">
-        <v>0.5239612874734439</v>
+        <v>1.297914892317856</v>
       </c>
       <c r="G43">
-        <v>-1.632098184414074</v>
+        <v>-1.956857088260115</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.067654701427218</v>
       </c>
       <c r="E44">
-        <v>-16.08397340565873</v>
+        <v>-18.81151858521866</v>
       </c>
       <c r="F44">
-        <v>0.4044626626803929</v>
+        <v>1.063235093635144</v>
       </c>
       <c r="G44">
-        <v>-0.9135762873268705</v>
+        <v>-1.404657030799604</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.030205003167851</v>
       </c>
       <c r="E45">
-        <v>-16.14989440178839</v>
+        <v>-17.84602528441331</v>
       </c>
       <c r="F45">
-        <v>0.2922520142971718</v>
+        <v>1.380571048503996</v>
       </c>
       <c r="G45">
-        <v>-1.346110194514432</v>
+        <v>-1.038019896190371</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.030610414343813</v>
       </c>
       <c r="E46">
-        <v>-15.42769789551913</v>
+        <v>-16.91152485971644</v>
       </c>
       <c r="F46">
-        <v>0.1736745340560338</v>
+        <v>1.344860129769309</v>
       </c>
       <c r="G46">
-        <v>-0.9650619348161175</v>
+        <v>-0.4139610865780208</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.056851451116758</v>
       </c>
       <c r="E47">
-        <v>-15.02371725776886</v>
+        <v>-17.08228455759768</v>
       </c>
       <c r="F47">
-        <v>0.09780270689882148</v>
+        <v>0.9850140165235928</v>
       </c>
       <c r="G47">
-        <v>-0.8201303785354443</v>
+        <v>-0.5343130121568935</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.103052083585332</v>
       </c>
       <c r="E48">
-        <v>-14.94103637933682</v>
+        <v>-16.22597276511725</v>
       </c>
       <c r="F48">
-        <v>-0.02894247593391968</v>
+        <v>0.7657700160246477</v>
       </c>
       <c r="G48">
-        <v>-0.7500992667922158</v>
+        <v>-0.2966803843787883</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.161098283503151</v>
       </c>
       <c r="E49">
-        <v>-14.44867351437885</v>
+        <v>-16.35664188260858</v>
       </c>
       <c r="F49">
-        <v>-0.1293687696449149</v>
+        <v>0.7511543015696531</v>
       </c>
       <c r="G49">
-        <v>-0.804390358714788</v>
+        <v>-1.027864515463889</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.229375327486609</v>
       </c>
       <c r="E50">
-        <v>-14.91946725763828</v>
+        <v>-15.85257744081479</v>
       </c>
       <c r="F50">
-        <v>-0.1336017270732204</v>
+        <v>1.208437958937064</v>
       </c>
       <c r="G50">
-        <v>-0.5821827534876325</v>
+        <v>-1.673592512254812</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.302231671270543</v>
       </c>
       <c r="E51">
-        <v>-14.04282714533743</v>
+        <v>-14.83201789607616</v>
       </c>
       <c r="F51">
-        <v>-0.04104823715843165</v>
+        <v>0.8344632112691994</v>
       </c>
       <c r="G51">
-        <v>-0.9373585811897257</v>
+        <v>-0.2901868469126472</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.379100587689671</v>
       </c>
       <c r="E52">
-        <v>-13.1867508335054</v>
+        <v>-16.22014009059537</v>
       </c>
       <c r="F52">
-        <v>-0.207030698759577</v>
+        <v>0.4753493748075577</v>
       </c>
       <c r="G52">
-        <v>-0.4741124402057613</v>
+        <v>-0.7859991118741004</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.456176524332951</v>
       </c>
       <c r="E53">
-        <v>-13.03029205654039</v>
+        <v>-14.23258832015484</v>
       </c>
       <c r="F53">
-        <v>-0.3408733334995043</v>
+        <v>0.6121418258688541</v>
       </c>
       <c r="G53">
-        <v>-0.5123058591576978</v>
+        <v>-1.593297739473641</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.530772643620717</v>
       </c>
       <c r="E54">
-        <v>-12.48841032830854</v>
+        <v>-13.13094191983487</v>
       </c>
       <c r="F54">
-        <v>-0.3347301608403432</v>
+        <v>0.5363785148414085</v>
       </c>
       <c r="G54">
-        <v>-0.9415060452408639</v>
+        <v>-1.188650934319799</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.600597760683407</v>
       </c>
       <c r="E55">
-        <v>-12.96259137012572</v>
+        <v>-14.98450972981045</v>
       </c>
       <c r="F55">
-        <v>-0.5231796031402167</v>
+        <v>0.9561984280498091</v>
       </c>
       <c r="G55">
-        <v>-1.25299897032207</v>
+        <v>-0.965803490888552</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.662173200550975</v>
       </c>
       <c r="E56">
-        <v>-12.13427913243472</v>
+        <v>-14.00163614576366</v>
       </c>
       <c r="F56">
-        <v>-0.1457563619744976</v>
+        <v>0.6189278116325877</v>
       </c>
       <c r="G56">
-        <v>-1.054727876371063</v>
+        <v>-1.513186715099798</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.715928606809777</v>
       </c>
       <c r="E57">
-        <v>-12.28203418235698</v>
+        <v>-12.69264903452849</v>
       </c>
       <c r="F57">
-        <v>-0.2779389484392147</v>
+        <v>0.3484882205384247</v>
       </c>
       <c r="G57">
-        <v>-1.721777250855258</v>
+        <v>-1.432508039396171</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.756439022825138</v>
       </c>
       <c r="E58">
-        <v>-11.28389511243033</v>
+        <v>-13.89495888356497</v>
       </c>
       <c r="F58">
-        <v>-0.3206959603021139</v>
+        <v>0.3053161966067228</v>
       </c>
       <c r="G58">
-        <v>-1.574762118884337</v>
+        <v>-1.693857336605943</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.781357087900895</v>
       </c>
       <c r="E59">
-        <v>-10.696266739773</v>
+        <v>-13.6048059684715</v>
       </c>
       <c r="F59">
-        <v>-0.297149616877538</v>
+        <v>0.7344610416684375</v>
       </c>
       <c r="G59">
-        <v>-1.541828498092191</v>
+        <v>-1.009919514755286</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.785517335231741</v>
       </c>
       <c r="E60">
-        <v>-11.97163445997523</v>
+        <v>-12.66287884640206</v>
       </c>
       <c r="F60">
-        <v>-0.4204173133533268</v>
+        <v>0.5895116567917744</v>
       </c>
       <c r="G60">
-        <v>-2.519169870566834</v>
+        <v>-1.537556347621794</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.768287423454654</v>
       </c>
       <c r="E61">
-        <v>-11.66476241884545</v>
+        <v>-13.04490997063715</v>
       </c>
       <c r="F61">
-        <v>-0.3449489011212779</v>
+        <v>0.8031691475262397</v>
       </c>
       <c r="G61">
-        <v>-2.681524713328159</v>
+        <v>-2.592741420372703</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.726325477861222</v>
       </c>
       <c r="E62">
-        <v>-10.54320884678775</v>
+        <v>-12.26433690593501</v>
       </c>
       <c r="F62">
-        <v>-0.5504544282447932</v>
+        <v>0.2020419757649029</v>
       </c>
       <c r="G62">
-        <v>-2.272704194350704</v>
+        <v>-2.235816701579426</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.660424945297641</v>
       </c>
       <c r="E63">
-        <v>-10.44298466004999</v>
+        <v>-12.40451581884244</v>
       </c>
       <c r="F63">
-        <v>-0.5970202734257647</v>
+        <v>0.246791211231535</v>
       </c>
       <c r="G63">
-        <v>-3.244444521623375</v>
+        <v>-3.065424354561631</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.569380138749973</v>
       </c>
       <c r="E64">
-        <v>-10.6976841521374</v>
+        <v>-12.62741183797399</v>
       </c>
       <c r="F64">
-        <v>-0.5242970707665933</v>
+        <v>-0.00206526718268692</v>
       </c>
       <c r="G64">
-        <v>-2.755739382559679</v>
+        <v>-2.911731936717241</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.455608205906906</v>
       </c>
       <c r="E65">
-        <v>-10.81663357889688</v>
+        <v>-12.99823498904009</v>
       </c>
       <c r="F65">
-        <v>-0.6903474584947681</v>
+        <v>0.03842201799654172</v>
       </c>
       <c r="G65">
-        <v>-3.168454711528195</v>
+        <v>-3.750415448532869</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.319923346331922</v>
       </c>
       <c r="E66">
-        <v>-10.20085621180787</v>
+        <v>-12.86005766164404</v>
       </c>
       <c r="F66">
-        <v>-0.6673793155173462</v>
+        <v>0.2508038229306958</v>
       </c>
       <c r="G66">
-        <v>-3.601100180248778</v>
+        <v>-3.59299556299695</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.164526905200404</v>
       </c>
       <c r="E67">
-        <v>-10.11032748792053</v>
+        <v>-12.72951081295092</v>
       </c>
       <c r="F67">
-        <v>-0.7773368045649526</v>
+        <v>0.2633950074532482</v>
       </c>
       <c r="G67">
-        <v>-3.59423258352486</v>
+        <v>-3.953808529338169</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.993601718104951</v>
       </c>
       <c r="E68">
-        <v>-10.00621334201018</v>
+        <v>-12.04788037684237</v>
       </c>
       <c r="F68">
-        <v>-0.8245761124444</v>
+        <v>-0.36074752422747</v>
       </c>
       <c r="G68">
-        <v>-3.559110387952564</v>
+        <v>-3.076258948150917</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.809440120080542</v>
       </c>
       <c r="E69">
-        <v>-10.24427974906742</v>
+        <v>-11.89675161378439</v>
       </c>
       <c r="F69">
-        <v>-1.075723026727363</v>
+        <v>-0.3628540625327892</v>
       </c>
       <c r="G69">
-        <v>-3.947547958602748</v>
+        <v>-2.90163233675727</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.620534789513085</v>
       </c>
       <c r="E70">
-        <v>-9.973409076298621</v>
+        <v>-12.10467196937257</v>
       </c>
       <c r="F70">
-        <v>-0.987787685083181</v>
+        <v>-0.9556097533214343</v>
       </c>
       <c r="G70">
-        <v>-3.232543531027269</v>
+        <v>-3.514603898720256</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.42886891628567</v>
       </c>
       <c r="E71">
-        <v>-10.18048713572137</v>
+        <v>-13.13606362393755</v>
       </c>
       <c r="F71">
-        <v>-0.8046969515120175</v>
+        <v>-0.3839906851826214</v>
       </c>
       <c r="G71">
-        <v>-4.40762443956029</v>
+        <v>-3.510689401399838</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.241799054709856</v>
       </c>
       <c r="E72">
-        <v>-10.9496575028722</v>
+        <v>-12.86527446370088</v>
       </c>
       <c r="F72">
-        <v>-1.086331928055016</v>
+        <v>-0.2357071215096903</v>
       </c>
       <c r="G72">
-        <v>-3.666534300587225</v>
+        <v>-3.911526708323164</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.059060891995073</v>
       </c>
       <c r="E73">
-        <v>-10.36456054718515</v>
+        <v>-12.74440043548814</v>
       </c>
       <c r="F73">
-        <v>-1.323595404667059</v>
+        <v>-0.2571477549963499</v>
       </c>
       <c r="G73">
-        <v>-3.366059717502634</v>
+        <v>-3.967077789324563</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.885306386788963</v>
       </c>
       <c r="E74">
-        <v>-11.08082928097838</v>
+        <v>-12.44944280947254</v>
       </c>
       <c r="F74">
-        <v>-1.163795048993006</v>
+        <v>-0.7279404279686154</v>
       </c>
       <c r="G74">
-        <v>-3.69474952477689</v>
+        <v>-3.745733145367542</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.72117814354077</v>
       </c>
       <c r="E75">
-        <v>-11.47096637368719</v>
+        <v>-13.31247032890634</v>
       </c>
       <c r="F75">
-        <v>-1.397284483717894</v>
+        <v>-0.7622083306876253</v>
       </c>
       <c r="G75">
-        <v>-3.79839347017507</v>
+        <v>-3.90647362712162</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.571860286388286</v>
       </c>
       <c r="E76">
-        <v>-11.31993270858337</v>
+        <v>-14.04124670790875</v>
       </c>
       <c r="F76">
-        <v>-1.681325867566025</v>
+        <v>-1.015938094532517</v>
       </c>
       <c r="G76">
-        <v>-3.865868510323491</v>
+        <v>-3.336407318269933</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.440156076032923</v>
       </c>
       <c r="E77">
-        <v>-12.63568083151199</v>
+        <v>-14.3476885440078</v>
       </c>
       <c r="F77">
-        <v>-1.749966875664201</v>
+        <v>-0.9545883763137825</v>
       </c>
       <c r="G77">
-        <v>-3.453819269331543</v>
+        <v>-3.08191905534096</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.333268693543518</v>
       </c>
       <c r="E78">
-        <v>-12.02825397049313</v>
+        <v>-14.64538589679804</v>
       </c>
       <c r="F78">
-        <v>-1.615515390883216</v>
+        <v>-1.092591900517972</v>
       </c>
       <c r="G78">
-        <v>-3.382134421922354</v>
+        <v>-3.727177837448882</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.255470071599552</v>
       </c>
       <c r="E79">
-        <v>-13.0322483573117</v>
+        <v>-14.96846987487529</v>
       </c>
       <c r="F79">
-        <v>-1.583197465030396</v>
+        <v>-1.486214694612838</v>
       </c>
       <c r="G79">
-        <v>-3.635021448730318</v>
+        <v>-4.008644304039609</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.216693440743371</v>
       </c>
       <c r="E80">
-        <v>-13.46401571157303</v>
+        <v>-15.25723254844839</v>
       </c>
       <c r="F80">
-        <v>-1.782759456038824</v>
+        <v>-0.8640213114309069</v>
       </c>
       <c r="G80">
-        <v>-3.120319191251141</v>
+        <v>-4.25818120363538</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.222464676628874</v>
       </c>
       <c r="E81">
-        <v>-13.74884314123347</v>
+        <v>-15.51073199492377</v>
       </c>
       <c r="F81">
-        <v>-1.977259293848746</v>
+        <v>-1.168166343777579</v>
       </c>
       <c r="G81">
-        <v>-2.471106537164088</v>
+        <v>-3.083434979701423</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.282350051427498</v>
       </c>
       <c r="E82">
-        <v>-15.28390978882758</v>
+        <v>-16.84064971302239</v>
       </c>
       <c r="F82">
-        <v>-2.009407404383992</v>
+        <v>-1.22584887950412</v>
       </c>
       <c r="G82">
-        <v>-3.206743285905356</v>
+        <v>-3.056394432830039</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.401129811451887</v>
       </c>
       <c r="E83">
-        <v>-15.03757891670634</v>
+        <v>-17.33731462828765</v>
       </c>
       <c r="F83">
-        <v>-2.111958460483168</v>
+        <v>-1.504218431745282</v>
       </c>
       <c r="G83">
-        <v>-3.036329762994035</v>
+        <v>-3.410090429608823</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.5844984006465</v>
       </c>
       <c r="E84">
-        <v>-16.69322524170269</v>
+        <v>-18.9981596414448</v>
       </c>
       <c r="F84">
-        <v>-2.303470377071191</v>
+        <v>-1.258510577829101</v>
       </c>
       <c r="G84">
-        <v>-2.321988142173564</v>
+        <v>-2.935789853191089</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.834800833599858</v>
       </c>
       <c r="E85">
-        <v>-18.07800995087824</v>
+        <v>-18.1975978924728</v>
       </c>
       <c r="F85">
-        <v>-2.155037707265756</v>
+        <v>-1.34149476750675</v>
       </c>
       <c r="G85">
-        <v>-2.50885370998394</v>
+        <v>-3.310968007519557</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.152898793211669</v>
       </c>
       <c r="E86">
-        <v>-18.11534269059748</v>
+        <v>-20.70265461556188</v>
       </c>
       <c r="F86">
-        <v>-2.199711561298733</v>
+        <v>-2.125913137750728</v>
       </c>
       <c r="G86">
-        <v>-2.511770715950286</v>
+        <v>-3.378915543572539</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.538540125651548</v>
       </c>
       <c r="E87">
-        <v>-19.63226374284285</v>
+        <v>-22.20532456010512</v>
       </c>
       <c r="F87">
-        <v>-2.161772334250516</v>
+        <v>-1.688193033335233</v>
       </c>
       <c r="G87">
-        <v>-2.353441932042401</v>
+        <v>-1.867407707328093</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.989431142654024</v>
       </c>
       <c r="E88">
-        <v>-21.82324815112995</v>
+        <v>-22.60002635461366</v>
       </c>
       <c r="F88">
-        <v>-2.241434770642939</v>
+        <v>-1.59209330256906</v>
       </c>
       <c r="G88">
-        <v>-1.641823725116268</v>
+        <v>-1.672217680421405</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.504796817760672</v>
       </c>
       <c r="E89">
-        <v>-23.24090052465318</v>
+        <v>-24.67528108116074</v>
       </c>
       <c r="F89">
-        <v>-2.4620149277626</v>
+        <v>-0.9564629717463177</v>
       </c>
       <c r="G89">
-        <v>-2.719941255346138</v>
+        <v>-2.849894035207945</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.078583532720363</v>
       </c>
       <c r="E90">
-        <v>-23.92418838224854</v>
+        <v>-27.51407728166711</v>
       </c>
       <c r="F90">
-        <v>-2.553555324343765</v>
+        <v>-1.470575118047983</v>
       </c>
       <c r="G90">
-        <v>-2.281110683986001</v>
+        <v>-2.540166407325721</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.710906428603737</v>
       </c>
       <c r="E91">
-        <v>-26.30896430721988</v>
+        <v>-27.49655208725743</v>
       </c>
       <c r="F91">
-        <v>-2.475854461961171</v>
+        <v>-1.572843700862805</v>
       </c>
       <c r="G91">
-        <v>-2.48060895480024</v>
+        <v>-3.230154801731993</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.390648208387933</v>
       </c>
       <c r="E92">
-        <v>-28.2937944647818</v>
+        <v>-30.33823745418069</v>
       </c>
       <c r="F92">
-        <v>-2.610600845537553</v>
+        <v>-1.071308656837844</v>
       </c>
       <c r="G92">
-        <v>-1.940447699241332</v>
+        <v>-3.023916901834656</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.11900528586075</v>
       </c>
       <c r="E93">
-        <v>-29.95232316348403</v>
+        <v>-31.16403638879744</v>
       </c>
       <c r="F93">
-        <v>-2.617095245975501</v>
+        <v>-1.566838865559911</v>
       </c>
       <c r="G93">
-        <v>-2.488434668219516</v>
+        <v>-2.230186125383419</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.876363961798408</v>
       </c>
       <c r="E94">
-        <v>-32.2477885240761</v>
+        <v>-32.91540333313091</v>
       </c>
       <c r="F94">
-        <v>-2.456837631495103</v>
+        <v>-1.139484122455646</v>
       </c>
       <c r="G94">
-        <v>-2.310986206284745</v>
+        <v>-3.120401221790127</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.65988389964294</v>
       </c>
       <c r="E95">
-        <v>-34.73203464486294</v>
+        <v>-35.33029587449028</v>
       </c>
       <c r="F95">
-        <v>-2.259735891672988</v>
+        <v>-1.508061228126869</v>
       </c>
       <c r="G95">
-        <v>-2.921470602305673</v>
+        <v>-4.123047374931208</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.45204898517975</v>
       </c>
       <c r="E96">
-        <v>-36.32396081209735</v>
+        <v>-37.52079120758455</v>
       </c>
       <c r="F96">
-        <v>-2.388868429360598</v>
+        <v>-1.456075375029381</v>
       </c>
       <c r="G96">
-        <v>-2.993959348996925</v>
+        <v>-2.495568043889748</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.24074640919365</v>
       </c>
       <c r="E97">
-        <v>-39.11081088726174</v>
+        <v>-39.88962463981189</v>
       </c>
       <c r="F97">
-        <v>-2.465087342459583</v>
+        <v>-1.548655372701059</v>
       </c>
       <c r="G97">
-        <v>-3.180319608687147</v>
+        <v>-3.813664275312726</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.02026108717564</v>
       </c>
       <c r="E98">
-        <v>-41.55380034560169</v>
+        <v>-41.87795077930773</v>
       </c>
       <c r="F98">
-        <v>-2.459521541880173</v>
+        <v>-1.247897534664434</v>
       </c>
       <c r="G98">
-        <v>-3.730990616900957</v>
+        <v>-3.730193280062012</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.76264583468217</v>
       </c>
       <c r="E99">
-        <v>-43.72751315402353</v>
+        <v>-44.25639589761636</v>
       </c>
       <c r="F99">
-        <v>-2.316775614294956</v>
+        <v>-1.466862375348636</v>
       </c>
       <c r="G99">
-        <v>-3.689561913491408</v>
+        <v>-3.511696736418588</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.48521373714715</v>
       </c>
       <c r="E100">
-        <v>-46.41412545702813</v>
+        <v>-47.80071929156976</v>
       </c>
       <c r="F100">
-        <v>-2.342753216046749</v>
+        <v>-0.9429605830806858</v>
       </c>
       <c r="G100">
-        <v>-4.236210144073338</v>
+        <v>-3.945461101690942</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.12880394092514</v>
       </c>
       <c r="E101">
-        <v>-48.19767626613412</v>
+        <v>-48.79100938392261</v>
       </c>
       <c r="F101">
-        <v>-2.209485468284365</v>
+        <v>-1.502376971008859</v>
       </c>
       <c r="G101">
-        <v>-4.952330186979029</v>
+        <v>-5.052722441811799</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.76725168016835</v>
       </c>
       <c r="E102">
-        <v>-51.14172439164527</v>
+        <v>-51.85715648986557</v>
       </c>
       <c r="F102">
-        <v>-1.837422592582161</v>
+        <v>-1.375109088344951</v>
       </c>
       <c r="G102">
-        <v>-4.935392521289175</v>
+        <v>-4.998375569122716</v>
       </c>
     </row>
   </sheetData>
